--- a/d/2026-09-03_会员有效性分析.xlsx
+++ b/d/2026-09-03_会员有效性分析.xlsx
@@ -469,19 +469,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C2" t="n">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D2" t="n">
         <v>53</v>
       </c>
       <c r="E2" t="n">
-        <v>91.40000000000001</v>
+        <v>91.38</v>
       </c>
       <c r="F2" t="n">
-        <v>8.6</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -813,25 +813,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DJI北京首都机场授权体验店</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>21.43</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="9">
@@ -840,7 +840,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京西铁营万达</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -849,16 +849,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>6.67</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="10">
@@ -867,25 +867,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>华为北京西铁营万达</t>
+          <t>DJI北京首都机场授权体验店</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>15.79</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="11">
@@ -5433,7 +5433,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>138****9886</t>
+          <t>136****4066</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>华为北京西铁营万达</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5456,7 +5456,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>136****4066</t>
+          <t>138****9886</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京西铁营万达</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5681,12 +5681,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DJI北京首都机场授权体验店</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5694,20 +5694,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>136****4066</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京西铁营万达</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>136****4066</t>
+          <t>138****9886</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -5733,12 +5733,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>华为北京西铁营万达</t>
+          <t>DJI北京首都机场授权体验店</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5746,14 +5746,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>138****9886</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
